--- a/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
+++ b/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
@@ -286,7 +286,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
   <sheet name="Sheet1">
     <column index="1" property="Id"/>
     <column index="2" property="Name"/>

--- a/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
+++ b/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
@@ -262,7 +262,7 @@
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." prompt="Required field" sqref="A2:A5">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
@@ -271,6 +271,10 @@
     </dataValidation>
     <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="C2:C5">
       <formula1>LEN(TRIM(C2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Date as yyyy-MM-dd" sqref="D2:D5">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="E2:E5">
       <formula1>ISNUMBER(E2)</formula1>

--- a/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
+++ b/src/Excelsior.Tests/StyleTests.GlobalStyle.verified.xlsx
@@ -12,13 +12,8 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-MM-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -51,20 +46,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
-    <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
+    <xf fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1"/>
+    <xf fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="2" fillId="2" borderId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -93,153 +81,153 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Employee ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Full Name</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Email Address</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Hire Date</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Annual Salary</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Is Active</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">John Doe</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">john@company.com</t>
         </is>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="3">
         <v>43845</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="2">
         <v>75000</v>
       </c>
-      <c r="F2" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Full Time</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Jane Smith</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">jane@company.com</t>
         </is>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="3">
         <v>43546</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="2">
         <v>120000</v>
       </c>
-      <c r="F3" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="F3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Full Time</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Bob Johnson</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">bob@company.com</t>
         </is>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>44387</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="2">
         <v>45000</v>
       </c>
-      <c r="F4" s="5" t="b">
+      <c r="F4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Part Time</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Alice Brown</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">alice@company.com</t>
         </is>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="3">
         <v>43409</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="2">
         <v>95000</v>
       </c>
-      <c r="F5" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="F5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Contract</t>
         </is>
